--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J378"/>
+  <dimension ref="A1:J382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14050,6 +14050,150 @@
         <v>378.46</v>
       </c>
       <c r="J378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="C379" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="D379" t="n">
+        <v>388.97</v>
+      </c>
+      <c r="E379" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="F379" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="G379" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="H379" t="n">
+        <v>381.28</v>
+      </c>
+      <c r="I379" t="n">
+        <v>377.09</v>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="C380" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="D380" t="n">
+        <v>389.43</v>
+      </c>
+      <c r="E380" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="F380" t="n">
+        <v>382.19</v>
+      </c>
+      <c r="G380" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="H380" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="I380" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="C381" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="D381" t="n">
+        <v>390.53</v>
+      </c>
+      <c r="E381" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="F381" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="G381" t="n">
+        <v>384.02</v>
+      </c>
+      <c r="H381" t="n">
+        <v>382.13</v>
+      </c>
+      <c r="I381" t="n">
+        <v>377.43</v>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="C382" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="D382" t="n">
+        <v>390.29</v>
+      </c>
+      <c r="E382" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="F382" t="n">
+        <v>383.95</v>
+      </c>
+      <c r="G382" t="n">
+        <v>384.56</v>
+      </c>
+      <c r="H382" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="I382" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="J382" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14066,7 +14210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18039,6 +18183,46 @@
       </c>
       <c r="B397" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -18207,28 +18391,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1303474807653619</v>
+        <v>0.1253086781895159</v>
       </c>
       <c r="J2" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04586052527317963</v>
+        <v>0.04333398552824119</v>
       </c>
       <c r="M2" t="n">
-        <v>3.452124448044492</v>
+        <v>3.440459872886779</v>
       </c>
       <c r="N2" t="n">
-        <v>20.03278624532289</v>
+        <v>19.89026880967938</v>
       </c>
       <c r="O2" t="n">
-        <v>4.475800067621752</v>
+        <v>4.459850760920077</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6406272404923</v>
+        <v>381.6933956770619</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18285,28 +18469,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.131421374748851</v>
+        <v>0.1217289818766903</v>
       </c>
       <c r="J3" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K3" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03536047553059851</v>
+        <v>0.03089931050590411</v>
       </c>
       <c r="M3" t="n">
-        <v>4.218222090475227</v>
+        <v>4.226002196165426</v>
       </c>
       <c r="N3" t="n">
-        <v>26.70190222527912</v>
+        <v>26.66580727951922</v>
       </c>
       <c r="O3" t="n">
-        <v>5.167388336991824</v>
+        <v>5.163894584470061</v>
       </c>
       <c r="P3" t="n">
-        <v>381.8854308362461</v>
+        <v>381.9869394398516</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18363,28 +18547,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.119407193647218</v>
+        <v>0.1167666661556026</v>
       </c>
       <c r="J4" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03313504429672587</v>
+        <v>0.03241568818161333</v>
       </c>
       <c r="M4" t="n">
-        <v>3.950683692643209</v>
+        <v>3.92214653085016</v>
       </c>
       <c r="N4" t="n">
-        <v>23.57775664386022</v>
+        <v>23.35167169880739</v>
       </c>
       <c r="O4" t="n">
-        <v>4.855693219702025</v>
+        <v>4.832356743743925</v>
       </c>
       <c r="P4" t="n">
-        <v>387.9176182215368</v>
+        <v>387.9452659792813</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18441,28 +18625,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1908708586466034</v>
+        <v>0.1889177729711188</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K5" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.12219342542349</v>
+        <v>0.1223527991822239</v>
       </c>
       <c r="M5" t="n">
-        <v>3.00565665248888</v>
+        <v>2.984139416553796</v>
       </c>
       <c r="N5" t="n">
-        <v>14.83178694145281</v>
+        <v>14.68920662427154</v>
       </c>
       <c r="O5" t="n">
-        <v>3.851205907433775</v>
+        <v>3.832650078505934</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7458802115686</v>
+        <v>384.7663274331506</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18519,28 +18703,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08918902206132386</v>
+        <v>0.08668119235192434</v>
       </c>
       <c r="J6" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K6" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03360892816946548</v>
+        <v>0.03246628828132836</v>
       </c>
       <c r="M6" t="n">
-        <v>2.867304783755295</v>
+        <v>2.850245336381094</v>
       </c>
       <c r="N6" t="n">
-        <v>12.96236613740602</v>
+        <v>12.84783236827137</v>
       </c>
       <c r="O6" t="n">
-        <v>3.600328615196955</v>
+        <v>3.584387307235557</v>
       </c>
       <c r="P6" t="n">
-        <v>381.83812660375</v>
+        <v>381.8643812694919</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18597,28 +18781,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003866537589264716</v>
+        <v>0.004396841926115356</v>
       </c>
       <c r="J7" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K7" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L7" t="n">
-        <v>8.300000593697288e-05</v>
+        <v>0.0001097436100206961</v>
       </c>
       <c r="M7" t="n">
-        <v>2.543505281382307</v>
+        <v>2.524573112071474</v>
       </c>
       <c r="N7" t="n">
-        <v>10.2068923830627</v>
+        <v>10.10651538414556</v>
       </c>
       <c r="O7" t="n">
-        <v>3.194822746736147</v>
+        <v>3.179074611289512</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1914615753965</v>
+        <v>383.1858901078156</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18675,28 +18859,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001784367927034677</v>
+        <v>-0.005392340029963219</v>
       </c>
       <c r="J8" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K8" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L8" t="n">
-        <v>1.374061091508061e-05</v>
+        <v>0.0001280117102436806</v>
       </c>
       <c r="M8" t="n">
-        <v>2.935371852806195</v>
+        <v>2.920934753339348</v>
       </c>
       <c r="N8" t="n">
-        <v>13.1316724454638</v>
+        <v>13.03154430286121</v>
       </c>
       <c r="O8" t="n">
-        <v>3.623764954500194</v>
+        <v>3.609923032816796</v>
       </c>
       <c r="P8" t="n">
-        <v>383.4940424258578</v>
+        <v>383.5318240909202</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18753,28 +18937,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03001847165533438</v>
+        <v>-0.03447445432808239</v>
       </c>
       <c r="J9" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="K9" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00467578292175197</v>
+        <v>0.006269522113209414</v>
       </c>
       <c r="M9" t="n">
-        <v>2.706707135311825</v>
+        <v>2.701791539994613</v>
       </c>
       <c r="N9" t="n">
-        <v>10.87052748868241</v>
+        <v>10.80875357580161</v>
       </c>
       <c r="O9" t="n">
-        <v>3.297048299416072</v>
+        <v>3.287666889421982</v>
       </c>
       <c r="P9" t="n">
-        <v>380.1575385281379</v>
+        <v>380.2042087717223</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18812,7 +18996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J378"/>
+  <dimension ref="A1:J382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38471,6 +38655,214 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-36.7275846975195,175.6860317134856</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-36.727683671186824,175.6869225384067</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-36.72767059164059,175.68780697920585</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-36.72767016019543,175.68868268676334</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-36.72770395871939,175.68958583201405</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-36.727707719268835,175.69048640488674</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-36.727716760241385,175.69137318683235</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-36.727698242927055,175.6922649056307</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-36.72758146666667,175.68603206248991</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-36.72767559405439,175.68692341085676</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-36.72766644960901,175.68780713317793</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-36.72767187061799,175.68868276575677</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-36.72770503935445,175.6895858675029</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-36.72770916042632,175.69048643410702</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>-36.72772197495834,175.69137359166746</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>-36.727705325673604,175.69226576766314</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-36.72757249207551,175.6860330319462</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-36.7276632988639,175.6869247389194</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-36.72765654475089,175.68780750137202</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-36.72766232826057,175.68868232505667</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-36.72769333247463,175.6895854830403</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-36.72769763116638,175.69048620034496</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-36.72770911798378,175.6913725935396</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-36.72769519465639,175.69226453462946</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-36.727569709952235,175.68603333247762</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-36.72765988851908,175.6869251072871</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-36.72765870581084,175.68780742103877</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-36.72765890741546,175.68868216706989</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-36.727689190040216,175.68958534699973</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-36.727692767259825,175.69048610172666</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-36.727705251900495,175.69137229340333</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-36.72769187742066,175.69226413089285</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14196,6 +14196,42 @@
       <c r="J382" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="C383" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="D383" t="n">
+        <v>392.89</v>
+      </c>
+      <c r="E383" t="n">
+        <v>391.73</v>
+      </c>
+      <c r="F383" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="G383" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="H383" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="I383" t="n">
+        <v>379.63</v>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18223,6 +18259,16 @@
       </c>
       <c r="B401" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -18391,28 +18437,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1253086781895159</v>
+        <v>0.125496345428368</v>
       </c>
       <c r="J2" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04333398552824119</v>
+        <v>0.04369243031038283</v>
       </c>
       <c r="M2" t="n">
-        <v>3.440459872886779</v>
+        <v>3.432468008603372</v>
       </c>
       <c r="N2" t="n">
-        <v>19.89026880967938</v>
+        <v>19.83855857420674</v>
       </c>
       <c r="O2" t="n">
-        <v>4.459850760920077</v>
+        <v>4.454049682503187</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6933956770619</v>
+        <v>381.6914249849449</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18469,28 +18515,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1217289818766903</v>
+        <v>0.1211338057298715</v>
       </c>
       <c r="J3" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03089931050590411</v>
+        <v>0.03077078356036911</v>
       </c>
       <c r="M3" t="n">
-        <v>4.226002196165426</v>
+        <v>4.218116333819417</v>
       </c>
       <c r="N3" t="n">
-        <v>26.66580727951922</v>
+        <v>26.59960762710079</v>
       </c>
       <c r="O3" t="n">
-        <v>5.163894584470061</v>
+        <v>5.157480744229763</v>
       </c>
       <c r="P3" t="n">
-        <v>381.9869394398516</v>
+        <v>381.9931893796275</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18547,28 +18593,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1167666661556026</v>
+        <v>0.1176833721998827</v>
       </c>
       <c r="J4" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K4" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03241568818161333</v>
+        <v>0.03307799213821971</v>
       </c>
       <c r="M4" t="n">
-        <v>3.92214653085016</v>
+        <v>3.916850378353297</v>
       </c>
       <c r="N4" t="n">
-        <v>23.35167169880739</v>
+        <v>23.29909647147514</v>
       </c>
       <c r="O4" t="n">
-        <v>4.832356743743925</v>
+        <v>4.826913762589419</v>
       </c>
       <c r="P4" t="n">
-        <v>387.9452659792813</v>
+        <v>387.9356396567219</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18625,28 +18671,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1889177729711188</v>
+        <v>0.1898771779463213</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K5" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1223527991822239</v>
+        <v>0.1239867178324726</v>
       </c>
       <c r="M5" t="n">
-        <v>2.984139416553796</v>
+        <v>2.98130234716075</v>
       </c>
       <c r="N5" t="n">
-        <v>14.68920662427154</v>
+        <v>14.6601235097271</v>
       </c>
       <c r="O5" t="n">
-        <v>3.832650078505934</v>
+        <v>3.828854072660265</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7663274331506</v>
+        <v>384.7562527294722</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18703,28 +18749,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08668119235192434</v>
+        <v>0.08756850088593723</v>
       </c>
       <c r="J6" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K6" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03246628828132836</v>
+        <v>0.03327309293881187</v>
       </c>
       <c r="M6" t="n">
-        <v>2.850245336381094</v>
+        <v>2.847333913264725</v>
       </c>
       <c r="N6" t="n">
-        <v>12.84783236827137</v>
+        <v>12.82221421856876</v>
       </c>
       <c r="O6" t="n">
-        <v>3.584387307235557</v>
+        <v>3.580811949623822</v>
       </c>
       <c r="P6" t="n">
-        <v>381.8643812694919</v>
+        <v>381.8550636499436</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18781,28 +18827,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004396841926115356</v>
+        <v>0.006111181703856462</v>
       </c>
       <c r="J7" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K7" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001097436100206961</v>
+        <v>0.0002125516390102389</v>
       </c>
       <c r="M7" t="n">
-        <v>2.524573112071474</v>
+        <v>2.526984084730448</v>
       </c>
       <c r="N7" t="n">
-        <v>10.10651538414556</v>
+        <v>10.10997730120991</v>
       </c>
       <c r="O7" t="n">
-        <v>3.179074611289512</v>
+        <v>3.179619049699179</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1858901078156</v>
+        <v>383.1678878400441</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18859,28 +18905,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.005392340029963219</v>
+        <v>-0.004828771719047578</v>
       </c>
       <c r="J8" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K8" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001280117102436806</v>
+        <v>0.0001032094747736023</v>
       </c>
       <c r="M8" t="n">
-        <v>2.920934753339348</v>
+        <v>2.916547349690465</v>
       </c>
       <c r="N8" t="n">
-        <v>13.03154430286121</v>
+        <v>13.0006635899515</v>
       </c>
       <c r="O8" t="n">
-        <v>3.609923032816796</v>
+        <v>3.605643297658755</v>
       </c>
       <c r="P8" t="n">
-        <v>383.5318240909202</v>
+        <v>383.5259060647667</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18937,28 +18983,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03447445432808239</v>
+        <v>-0.03429933552074805</v>
       </c>
       <c r="J9" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K9" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006269522113209414</v>
+        <v>0.00624107234031579</v>
       </c>
       <c r="M9" t="n">
-        <v>2.701791539994613</v>
+        <v>2.695598645083993</v>
       </c>
       <c r="N9" t="n">
-        <v>10.80875357580161</v>
+        <v>10.78077059680795</v>
       </c>
       <c r="O9" t="n">
-        <v>3.287666889421982</v>
+        <v>3.28340838105892</v>
       </c>
       <c r="P9" t="n">
-        <v>380.2042087717223</v>
+        <v>380.2023698505806</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18996,7 +19042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38863,6 +38909,58 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-36.72755211975351,175.68603523261146</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-36.72763960594202,175.68692729810496</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-36.727635294327975,175.68780829131566</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-36.72764018278952,175.68868130230058</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-36.72767126950875,175.68958475847677</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-36.727673491778255,175.69048571090624</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-36.72768780957127,175.69137093930073</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-36.727675470551965,175.6922621340341</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0160/nzd0160.xlsx
+++ b/data/nzd0160/nzd0160.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J383"/>
+  <dimension ref="A1:J384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14232,6 +14232,42 @@
       <c r="J383" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="C384" t="n">
+        <v>383.69</v>
+      </c>
+      <c r="D384" t="n">
+        <v>392.01</v>
+      </c>
+      <c r="E384" t="n">
+        <v>391.94</v>
+      </c>
+      <c r="F384" t="n">
+        <v>385.89</v>
+      </c>
+      <c r="G384" t="n">
+        <v>386.67</v>
+      </c>
+      <c r="H384" t="n">
+        <v>384.21</v>
+      </c>
+      <c r="I384" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18269,6 +18305,16 @@
       </c>
       <c r="B402" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -18437,28 +18483,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.125496345428368</v>
+        <v>0.1258501393039893</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K2" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04369243031038283</v>
+        <v>0.04416505084575972</v>
       </c>
       <c r="M2" t="n">
-        <v>3.432468008603372</v>
+        <v>3.425394945387651</v>
       </c>
       <c r="N2" t="n">
-        <v>19.83855857420674</v>
+        <v>19.78802778458839</v>
       </c>
       <c r="O2" t="n">
-        <v>4.454049682503187</v>
+        <v>4.448373611173908</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6914249849449</v>
+        <v>381.6876918851679</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18515,28 +18561,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1211338057298715</v>
+        <v>0.1203450670265819</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03077078356036911</v>
+        <v>0.03054446541305122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.218116333819417</v>
+        <v>4.211265878420872</v>
       </c>
       <c r="N3" t="n">
-        <v>26.59960762710079</v>
+        <v>26.53645414603902</v>
       </c>
       <c r="O3" t="n">
-        <v>5.157480744229763</v>
+        <v>5.151354593312231</v>
       </c>
       <c r="P3" t="n">
-        <v>381.9931893796275</v>
+        <v>382.0015118534755</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18593,28 +18639,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1176833721998827</v>
+        <v>0.1181413194475849</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03307799213821971</v>
+        <v>0.03350807383709564</v>
       </c>
       <c r="M4" t="n">
-        <v>3.916850378353297</v>
+        <v>3.909076095702244</v>
       </c>
       <c r="N4" t="n">
-        <v>23.29909647147514</v>
+        <v>23.24038613329819</v>
       </c>
       <c r="O4" t="n">
-        <v>4.826913762589419</v>
+        <v>4.820828365882589</v>
       </c>
       <c r="P4" t="n">
-        <v>387.9356396567219</v>
+        <v>387.9308075697749</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18671,28 +18717,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1898771779463213</v>
+        <v>0.1909270558850365</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1239867178324726</v>
+        <v>0.1257297642571807</v>
       </c>
       <c r="M5" t="n">
-        <v>2.98130234716075</v>
+        <v>2.978891371368008</v>
       </c>
       <c r="N5" t="n">
-        <v>14.6601235097271</v>
+        <v>14.63300370203137</v>
       </c>
       <c r="O5" t="n">
-        <v>3.828854072660265</v>
+        <v>3.825310928804529</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7562527294722</v>
+        <v>384.7451748127272</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18749,28 +18795,28 @@
         <v>0.1847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08756850088593723</v>
+        <v>0.08841664078288491</v>
       </c>
       <c r="J6" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K6" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03327309293881187</v>
+        <v>0.03406679209363994</v>
       </c>
       <c r="M6" t="n">
-        <v>2.847333913264725</v>
+        <v>2.844196555833111</v>
       </c>
       <c r="N6" t="n">
-        <v>12.82221421856876</v>
+        <v>12.79601726419265</v>
       </c>
       <c r="O6" t="n">
-        <v>3.580811949623822</v>
+        <v>3.577152116445798</v>
       </c>
       <c r="P6" t="n">
-        <v>381.8550636499436</v>
+        <v>381.8461143970638</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18827,28 +18873,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006111181703856462</v>
+        <v>0.007800249067927569</v>
       </c>
       <c r="J7" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K7" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002125516390102389</v>
+        <v>0.0003472164447363424</v>
       </c>
       <c r="M7" t="n">
-        <v>2.526984084730448</v>
+        <v>2.529271554481045</v>
       </c>
       <c r="N7" t="n">
-        <v>10.10997730120991</v>
+        <v>10.11245898782288</v>
       </c>
       <c r="O7" t="n">
-        <v>3.179619049699179</v>
+        <v>3.180009274801393</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1678878400441</v>
+        <v>383.1500654371285</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18905,28 +18951,28 @@
         <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.004828771719047578</v>
+        <v>-0.004416625050646042</v>
       </c>
       <c r="J8" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K8" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001032094747736023</v>
+        <v>8.68253610545322e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.916547349690465</v>
+        <v>2.911288574493927</v>
       </c>
       <c r="N8" t="n">
-        <v>13.0006635899515</v>
+        <v>12.9684387273668</v>
       </c>
       <c r="O8" t="n">
-        <v>3.605643297658755</v>
+        <v>3.601171854739343</v>
       </c>
       <c r="P8" t="n">
-        <v>383.5259060647667</v>
+        <v>383.5215572482891</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18983,28 +19029,28 @@
         <v>0.1574</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03429933552074805</v>
+        <v>-0.03379347552195741</v>
       </c>
       <c r="J9" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K9" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00624107234031579</v>
+        <v>0.0060923339077259</v>
       </c>
       <c r="M9" t="n">
-        <v>2.695598645083993</v>
+        <v>2.691071167053578</v>
       </c>
       <c r="N9" t="n">
-        <v>10.78077059680795</v>
+        <v>10.75521261830737</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28340838105892</v>
+        <v>3.279514082651174</v>
       </c>
       <c r="P9" t="n">
-        <v>380.2023698505806</v>
+        <v>380.1970322063225</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -19042,7 +19088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J383"/>
+  <dimension ref="A1:J384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38961,6 +39007,58 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-36.72754897864658,175.686035571921</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-36.72764301628684,175.6869269297374</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-36.727643218214496,175.6878079967604</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-36.72763829232245,175.6886812149922</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-36.72767171977336,175.6895847732638</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-36.7276737619953,175.69048571638504</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>-36.727690416929775,175.69137114171807</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>-36.72766964297563,175.6922614247676</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
